--- a/datasets/subsidy_dataset2_initial.xlsx
+++ b/datasets/subsidy_dataset2_initial.xlsx
@@ -81,7 +81,7 @@
     <t>Average Yield (bags/ha)</t>
   </si>
   <si>
-    <t>Yield (bags/ha)</t>
+    <t>Crop Yield (bags/ha)</t>
   </si>
   <si>
     <t>Average Selling Price (₱/kg)</t>
